--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8d900aa62abc4458"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R69925b38b3494074"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R69925b38b3494074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2a21bbbe06f04582"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2a21bbbe06f04582"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7a6822bc90d84534"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7a6822bc90d84534"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5b99663d558944fc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5b99663d558944fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra0bcba77515c4919"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra0bcba77515c4919"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R61ae073123984947"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R61ae073123984947"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ree3f786589d14f8b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ree3f786589d14f8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1200cb2763084c29"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1200cb2763084c29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5c5dc9c4a25940d8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5c5dc9c4a25940d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R00a1c478656445bf"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R00a1c478656445bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89978a5717734ca2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89978a5717734ca2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8422f80c8eeb43f8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8422f80c8eeb43f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R682dc1b58b5942db"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R682dc1b58b5942db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6d875b3c0e234867"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MergedCells/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6d875b3c0e234867"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rae275a5ed7844d7f"/>
   </x:sheets>
 </x:workbook>
 </file>
